--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -54,10 +54,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -437,6 +438,11 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +501,31 @@
           <t>modifie_le</t>
         </is>
       </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>periodicite</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>echeance</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>debut</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>faits</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -552,6 +583,11 @@
           <t>2026-09-23T13:00:00.000Z</t>
         </is>
       </c>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -601,6 +637,11 @@
           <t>2026-09-23T13:00:00.000Z</t>
         </is>
       </c>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Taches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Epics" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -443,6 +444,7 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,6 +526,11 @@
       <c r="P1" s="3" t="inlineStr">
         <is>
           <t>faits</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>epic</t>
         </is>
       </c>
     </row>
@@ -588,6 +595,7 @@
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -642,6 +650,73 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>debut</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>couleur</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>cree_le</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>modifie_le</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Taches" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Epics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Objectifs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Domaines" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -445,6 +447,8 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="38" customWidth="1" min="18" max="18"/>
+    <col width="38" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,6 +535,16 @@
       <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>epic</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>objectif</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>domaine</t>
         </is>
       </c>
     </row>
@@ -596,6 +610,8 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -651,6 +667,8 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -663,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -674,6 +692,8 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -713,6 +733,160 @@
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>modifie_le</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>objectif</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>domaine</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>domaine</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>debut</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>couleur</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>cible</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>actuel</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>unite</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>cree_le</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>modifie_le</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>icone</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>couleur</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>cree_le</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>modifie_le</t>
         </is>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -11,6 +11,8 @@
     <sheet name="Epics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Objectifs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Domaines" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Features" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ObjectifsPI" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -449,6 +451,9 @@
     <col width="38" customWidth="1" min="17" max="17"/>
     <col width="38" customWidth="1" min="18" max="18"/>
     <col width="38" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="38" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,6 +550,21 @@
       <c r="S1" s="3" t="inlineStr">
         <is>
           <t>domaine</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>iteration</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>feature</t>
         </is>
       </c>
     </row>
@@ -612,6 +632,9 @@
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -669,6 +692,9 @@
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -681,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -694,6 +720,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -745,6 +772,11 @@
       <c r="J1" s="3" t="inlineStr">
         <is>
           <t>domaine</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>etat</t>
         </is>
       </c>
     </row>
@@ -895,4 +927,148 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>iteration</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>couleur</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>cree_le</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>modifie_le</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>valeur_prevue</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>valeur_obtenue</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>cree_le</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>modifie_le</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -1013,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1024,6 +1024,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1065,6 +1066,11 @@
       <c r="H1" s="3" t="inlineStr">
         <is>
           <t>modifie_le</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>domaine</t>
         </is>
       </c>
     </row>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -565,6 +565,11 @@
       <c r="V1" s="3" t="inlineStr">
         <is>
           <t>feature</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>telephone</t>
         </is>
       </c>
     </row>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -570,6 +570,11 @@
       <c r="W1" s="3" t="inlineStr">
         <is>
           <t>telephone</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>parent</t>
         </is>
       </c>
     </row>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -575,6 +575,11 @@
       <c r="X1" s="3" t="inlineStr">
         <is>
           <t>parent</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>heure_fin</t>
         </is>
       </c>
     </row>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Domaines" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Features" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="ObjectifsPI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ignorees" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1092,4 +1093,52 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>cle</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>signature</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>cree_le</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>modifie_le</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1041,6 +1041,7 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1087,6 +1088,11 @@
       <c r="I1" s="3" t="inlineStr">
         <is>
           <t>domaine</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>epic</t>
         </is>
       </c>
     </row>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -455,6 +455,8 @@
     <col width="8" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="38" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -581,6 +583,11 @@
       <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>heure_fin</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>date_fin</t>
         </is>
       </c>
     </row>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -457,6 +457,7 @@
     <col width="38" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,6 +589,11 @@
       <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>date_fin</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>termine_le</t>
         </is>
       </c>
     </row>

--- a/modele/Taches.xlsx
+++ b/modele/Taches.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,7 @@
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -594,6 +595,11 @@
       <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>termine_le</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>statut_avant</t>
         </is>
       </c>
     </row>
